--- a/entry_list.xlsx
+++ b/entry_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="545">
   <si>
     <t>연락처 (*정확히 기재)(*)</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>2026-10-12 13:00:41</t>
-  </si>
-  <si>
-    <t>김예슬</t>
   </si>
   <si>
     <t>010-7748-7869</t>
@@ -1626,6 +1623,53 @@
   </si>
   <si>
     <t>김정길770114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예슬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이선호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조선휘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김진해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김찬희</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최승혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안재면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 철인 3종협회</t>
+  </si>
+  <si>
+    <t>서울시 철인 3종협회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갱년기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1978,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -2019,31 +2063,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2081,26 +2125,26 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" ref="D4:D67" si="0">RIGHT(C4, 4)</f>
         <v>7869</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -2108,13 +2152,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
@@ -2130,21 +2174,21 @@
         <v>6</v>
       </c>
       <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
         <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
@@ -2157,10 +2201,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
       </c>
       <c r="I6" t="s">
         <v>8</v>
@@ -2168,20 +2212,20 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
         <v>0347</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -2190,21 +2234,21 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
@@ -2214,13 +2258,13 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
         <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -2228,13 +2272,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
@@ -2244,27 +2288,27 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
         <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
@@ -2274,13 +2318,13 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
         <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" t="s">
-        <v>43</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
@@ -2288,20 +2332,20 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>6508</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -2310,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
@@ -2318,13 +2362,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
@@ -2340,21 +2384,21 @@
         <v>6</v>
       </c>
       <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
         <v>50</v>
-      </c>
-      <c r="I12" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
         <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -2364,27 +2408,27 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -2394,87 +2438,87 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
         <v>58</v>
       </c>
-      <c r="G14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" t="s">
-        <v>59</v>
-      </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
         <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
         <v>1928</v>
       </c>
       <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" t="s">
         <v>62</v>
-      </c>
-      <c r="I15" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
         <v>64</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
         <v>2342</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
         <v>67</v>
       </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>68</v>
-      </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -2484,27 +2528,27 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
         <v>72</v>
       </c>
-      <c r="G17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H17" t="s">
-        <v>73</v>
-      </c>
       <c r="I17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -2520,7 +2564,7 @@
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
         <v>8</v>
@@ -2528,13 +2572,13 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
         <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
@@ -2550,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s">
         <v>8</v>
@@ -2558,13 +2602,13 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
         <v>81</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
@@ -2580,21 +2624,21 @@
         <v>6</v>
       </c>
       <c r="H20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
@@ -2604,13 +2648,13 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s">
         <v>8</v>
@@ -2618,73 +2662,73 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
         <v>88</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
         <v>3619</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" t="s">
         <v>91</v>
       </c>
-      <c r="H22" t="s">
-        <v>92</v>
-      </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
         <v>93</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v>0901</v>
       </c>
       <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
       <c r="G23" t="s">
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
         <v>97</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
@@ -2697,10 +2741,10 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
         <v>8</v>
@@ -2708,20 +2752,20 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
         <v>100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
         <v>1217</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
@@ -2730,21 +2774,21 @@
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
         <v>102</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>103</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
@@ -2757,10 +2801,10 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s">
         <v>8</v>
@@ -2768,13 +2812,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
         <v>106</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>107</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
@@ -2790,7 +2834,7 @@
         <v>6</v>
       </c>
       <c r="H27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s">
         <v>8</v>
@@ -2798,13 +2842,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
         <v>109</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>110</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
@@ -2820,7 +2864,7 @@
         <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I28" t="s">
         <v>8</v>
@@ -2828,43 +2872,43 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
         <v>113</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
         <v>7064</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" t="s">
         <v>115</v>
       </c>
-      <c r="G29" t="s">
-        <v>6</v>
-      </c>
-      <c r="H29" t="s">
-        <v>116</v>
-      </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
         <v>117</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>118</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
@@ -2880,21 +2924,21 @@
         <v>6</v>
       </c>
       <c r="H30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" t="s">
         <v>121</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>122</v>
-      </c>
-      <c r="C31" t="s">
-        <v>123</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="0"/>
@@ -2904,43 +2948,43 @@
         <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" t="s">
         <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
         <v>125</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="0"/>
         <v>4709</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I32" t="s">
         <v>8</v>
@@ -2948,73 +2992,73 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
         <v>131</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>132</v>
-      </c>
-      <c r="C33" t="s">
-        <v>133</v>
       </c>
       <c r="D33" t="str">
         <f t="shared" si="0"/>
         <v>8721</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" t="s">
         <v>6</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
         <v>135</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>136</v>
-      </c>
-      <c r="C34" t="s">
-        <v>137</v>
       </c>
       <c r="D34" t="str">
         <f t="shared" si="0"/>
         <v>1786</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
         <v>138</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>139</v>
-      </c>
-      <c r="C35" t="s">
-        <v>140</v>
       </c>
       <c r="D35" t="str">
         <f t="shared" si="0"/>
@@ -3024,13 +3068,13 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G35" t="s">
         <v>6</v>
       </c>
       <c r="H35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I35" t="s">
         <v>8</v>
@@ -3038,43 +3082,43 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
         <v>142</v>
-      </c>
-      <c r="C36" t="s">
-        <v>143</v>
       </c>
       <c r="D36" t="str">
         <f t="shared" si="0"/>
         <v>2842</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" t="s">
         <v>145</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>146</v>
-      </c>
-      <c r="C37" t="s">
-        <v>147</v>
       </c>
       <c r="D37" t="str">
         <f t="shared" si="0"/>
@@ -3084,27 +3128,27 @@
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G37" t="s">
         <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" t="s">
         <v>149</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>150</v>
-      </c>
-      <c r="C38" t="s">
-        <v>151</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="0"/>
@@ -3120,21 +3164,21 @@
         <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" t="s">
         <v>152</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>153</v>
-      </c>
-      <c r="C39" t="s">
-        <v>154</v>
       </c>
       <c r="D39" t="str">
         <f t="shared" si="0"/>
@@ -3147,10 +3191,10 @@
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I39" t="s">
         <v>8</v>
@@ -3158,13 +3202,13 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
         <v>155</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>156</v>
-      </c>
-      <c r="C40" t="s">
-        <v>157</v>
       </c>
       <c r="D40" t="str">
         <f t="shared" si="0"/>
@@ -3174,27 +3218,27 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
+        <v>157</v>
+      </c>
+      <c r="G40" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" t="s">
         <v>158</v>
       </c>
-      <c r="G40" t="s">
-        <v>6</v>
-      </c>
-      <c r="H40" t="s">
-        <v>159</v>
-      </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" t="s">
         <v>160</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>161</v>
-      </c>
-      <c r="C41" t="s">
-        <v>162</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="0"/>
@@ -3207,24 +3251,24 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" t="s">
         <v>164</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>165</v>
-      </c>
-      <c r="C42" t="s">
-        <v>166</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="0"/>
@@ -3234,27 +3278,27 @@
         <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
         <v>6</v>
       </c>
       <c r="H42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
         <v>168</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>169</v>
-      </c>
-      <c r="C43" t="s">
-        <v>170</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="0"/>
@@ -3270,28 +3314,28 @@
         <v>6</v>
       </c>
       <c r="H43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" t="s">
         <v>172</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>173</v>
-      </c>
-      <c r="C44" t="s">
-        <v>174</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="0"/>
         <v>1197</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
@@ -3303,34 +3347,34 @@
         <v>7</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
         <v>175</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>176</v>
-      </c>
-      <c r="C45" t="s">
-        <v>177</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="0"/>
         <v>1118</v>
       </c>
       <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
         <v>12</v>
       </c>
-      <c r="F45" t="s">
-        <v>13</v>
-      </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I45" t="s">
         <v>8</v>
@@ -3338,13 +3382,13 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" t="s">
         <v>179</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>180</v>
-      </c>
-      <c r="C46" t="s">
-        <v>181</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="0"/>
@@ -3360,21 +3404,21 @@
         <v>6</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" t="s">
         <v>182</v>
-      </c>
-      <c r="C47" t="s">
-        <v>183</v>
       </c>
       <c r="D47" t="str">
         <f t="shared" si="0"/>
@@ -3387,24 +3431,24 @@
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" t="s">
         <v>185</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>186</v>
-      </c>
-      <c r="C48" t="s">
-        <v>187</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="0"/>
@@ -3423,18 +3467,18 @@
         <v>7</v>
       </c>
       <c r="I48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" t="s">
         <v>188</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>189</v>
-      </c>
-      <c r="C49" t="s">
-        <v>190</v>
       </c>
       <c r="D49" t="str">
         <f t="shared" si="0"/>
@@ -3447,10 +3491,10 @@
         <v>5</v>
       </c>
       <c r="G49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I49" t="s">
         <v>8</v>
@@ -3458,13 +3502,13 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" t="s">
         <v>86</v>
-      </c>
-      <c r="C50" t="s">
-        <v>87</v>
       </c>
       <c r="D50" t="str">
         <f t="shared" si="0"/>
@@ -3474,13 +3518,13 @@
         <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" t="s">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I50" t="s">
         <v>8</v>
@@ -3488,13 +3532,13 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" t="s">
         <v>192</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>193</v>
-      </c>
-      <c r="C51" t="s">
-        <v>194</v>
       </c>
       <c r="D51" t="str">
         <f t="shared" si="0"/>
@@ -3504,13 +3548,13 @@
         <v>4</v>
       </c>
       <c r="F51" t="s">
+        <v>194</v>
+      </c>
+      <c r="G51" t="s">
+        <v>6</v>
+      </c>
+      <c r="H51" t="s">
         <v>195</v>
-      </c>
-      <c r="G51" t="s">
-        <v>6</v>
-      </c>
-      <c r="H51" t="s">
-        <v>196</v>
       </c>
       <c r="I51" t="s">
         <v>8</v>
@@ -3518,13 +3562,13 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" t="s">
         <v>197</v>
-      </c>
-      <c r="C52" t="s">
-        <v>198</v>
       </c>
       <c r="D52" t="str">
         <f t="shared" si="0"/>
@@ -3534,13 +3578,13 @@
         <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
         <v>6</v>
       </c>
       <c r="H52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I52" t="s">
         <v>8</v>
@@ -3548,20 +3592,20 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
+        <v>199</v>
+      </c>
+      <c r="B53" t="s">
         <v>200</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>201</v>
-      </c>
-      <c r="C53" t="s">
-        <v>202</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="0"/>
         <v>4456</v>
       </c>
       <c r="E53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
@@ -3570,51 +3614,51 @@
         <v>6</v>
       </c>
       <c r="H53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" t="s">
         <v>204</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>205</v>
-      </c>
-      <c r="C54" t="s">
-        <v>206</v>
       </c>
       <c r="D54" t="str">
         <f t="shared" si="0"/>
         <v>5054</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54" t="s">
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" t="s">
         <v>207</v>
-      </c>
-      <c r="C55" t="s">
-        <v>208</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="0"/>
@@ -3627,54 +3671,54 @@
         <v>5</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" t="s">
         <v>210</v>
-      </c>
-      <c r="C56" t="s">
-        <v>211</v>
       </c>
       <c r="D56" t="str">
         <f t="shared" si="0"/>
         <v>6950</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" t="s">
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" t="s">
+        <v>532</v>
+      </c>
+      <c r="C57" t="s">
         <v>212</v>
-      </c>
-      <c r="B57" t="s">
-        <v>533</v>
-      </c>
-      <c r="C57" t="s">
-        <v>213</v>
       </c>
       <c r="D57" t="str">
         <f t="shared" si="0"/>
@@ -3690,21 +3734,21 @@
         <v>6</v>
       </c>
       <c r="H57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" t="s">
         <v>215</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>216</v>
-      </c>
-      <c r="C58" t="s">
-        <v>217</v>
       </c>
       <c r="D58" t="str">
         <f t="shared" si="0"/>
@@ -3714,27 +3758,27 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
+        <v>219</v>
+      </c>
+      <c r="B59" t="s">
         <v>220</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>221</v>
-      </c>
-      <c r="C59" t="s">
-        <v>222</v>
       </c>
       <c r="D59" t="str">
         <f t="shared" si="0"/>
@@ -3744,13 +3788,13 @@
         <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G59" t="s">
         <v>6</v>
       </c>
       <c r="H59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I59" t="s">
         <v>8</v>
@@ -3758,13 +3802,13 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
+        <v>223</v>
+      </c>
+      <c r="B60" t="s">
         <v>224</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>225</v>
-      </c>
-      <c r="C60" t="s">
-        <v>226</v>
       </c>
       <c r="D60" t="str">
         <f t="shared" si="0"/>
@@ -3780,21 +3824,21 @@
         <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
+        <v>226</v>
+      </c>
+      <c r="B61" t="s">
         <v>227</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>228</v>
-      </c>
-      <c r="C61" t="s">
-        <v>229</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" si="0"/>
@@ -3807,10 +3851,10 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I61" t="s">
         <v>8</v>
@@ -3818,13 +3862,13 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" t="s">
         <v>231</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>232</v>
-      </c>
-      <c r="C62" t="s">
-        <v>233</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="0"/>
@@ -3840,7 +3884,7 @@
         <v>6</v>
       </c>
       <c r="H62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I62" t="s">
         <v>8</v>
@@ -3848,43 +3892,43 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" t="s">
         <v>128</v>
-      </c>
-      <c r="C63" t="s">
-        <v>129</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="0"/>
         <v>7149</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F63" t="s">
+        <v>234</v>
+      </c>
+      <c r="G63" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" t="s">
         <v>235</v>
       </c>
-      <c r="G63" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" t="s">
-        <v>236</v>
-      </c>
       <c r="I63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" t="s">
         <v>237</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>238</v>
-      </c>
-      <c r="C64" t="s">
-        <v>239</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="0"/>
@@ -3894,13 +3938,13 @@
         <v>4</v>
       </c>
       <c r="F64" t="s">
+        <v>239</v>
+      </c>
+      <c r="G64" t="s">
+        <v>6</v>
+      </c>
+      <c r="H64" t="s">
         <v>240</v>
-      </c>
-      <c r="G64" t="s">
-        <v>6</v>
-      </c>
-      <c r="H64" t="s">
-        <v>241</v>
       </c>
       <c r="I64" t="s">
         <v>8</v>
@@ -3908,59 +3952,59 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
+        <v>241</v>
+      </c>
+      <c r="B65" t="s">
         <v>242</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>243</v>
-      </c>
-      <c r="C65" t="s">
-        <v>244</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" si="0"/>
         <v>0097</v>
       </c>
       <c r="E65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F65" t="s">
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" t="s">
         <v>247</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>248</v>
-      </c>
-      <c r="C66" t="s">
-        <v>249</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="0"/>
         <v>0604</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I66" t="s">
         <v>8</v>
@@ -3968,13 +4012,13 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
+        <v>250</v>
+      </c>
+      <c r="B67" t="s">
         <v>251</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>252</v>
-      </c>
-      <c r="C67" t="s">
-        <v>253</v>
       </c>
       <c r="D67" t="str">
         <f t="shared" si="0"/>
@@ -3990,21 +4034,21 @@
         <v>6</v>
       </c>
       <c r="H67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" t="s">
         <v>255</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>256</v>
-      </c>
-      <c r="C68" t="s">
-        <v>257</v>
       </c>
       <c r="D68" t="str">
         <f t="shared" ref="D68:D131" si="1">RIGHT(C68, 4)</f>
@@ -4023,18 +4067,18 @@
         <v>7</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" t="s">
         <v>258</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>259</v>
-      </c>
-      <c r="C69" t="s">
-        <v>260</v>
       </c>
       <c r="D69" t="str">
         <f t="shared" si="1"/>
@@ -4044,27 +4088,27 @@
         <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G69" t="s">
         <v>6</v>
       </c>
       <c r="H69" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" t="s">
         <v>262</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>263</v>
-      </c>
-      <c r="C70" t="s">
-        <v>264</v>
       </c>
       <c r="D70" t="str">
         <f t="shared" si="1"/>
@@ -4077,24 +4121,24 @@
         <v>5</v>
       </c>
       <c r="G70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" t="s">
         <v>265</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>266</v>
-      </c>
-      <c r="C71" t="s">
-        <v>267</v>
       </c>
       <c r="D71" t="str">
         <f t="shared" si="1"/>
@@ -4104,27 +4148,27 @@
         <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G71" t="s">
         <v>6</v>
       </c>
       <c r="H71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" t="s">
         <v>269</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>270</v>
-      </c>
-      <c r="C72" t="s">
-        <v>271</v>
       </c>
       <c r="D72" t="str">
         <f t="shared" si="1"/>
@@ -4140,7 +4184,7 @@
         <v>6</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s">
         <v>8</v>
@@ -4148,43 +4192,43 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" t="s">
         <v>272</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>273</v>
-      </c>
-      <c r="C73" t="s">
-        <v>274</v>
       </c>
       <c r="D73" t="str">
         <f t="shared" si="1"/>
         <v>5918</v>
       </c>
       <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" t="s">
         <v>12</v>
       </c>
-      <c r="F73" t="s">
-        <v>13</v>
-      </c>
       <c r="G73" t="s">
         <v>6</v>
       </c>
       <c r="H73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" t="s">
         <v>276</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>277</v>
-      </c>
-      <c r="C74" t="s">
-        <v>278</v>
       </c>
       <c r="D74" t="str">
         <f t="shared" si="1"/>
@@ -4197,10 +4241,10 @@
         <v>5</v>
       </c>
       <c r="G74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I74" t="s">
         <v>8</v>
@@ -4208,20 +4252,20 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B75" t="s">
+        <v>279</v>
+      </c>
+      <c r="C75" t="s">
         <v>280</v>
-      </c>
-      <c r="C75" t="s">
-        <v>281</v>
       </c>
       <c r="D75" t="str">
         <f t="shared" si="1"/>
         <v>1913</v>
       </c>
       <c r="E75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F75" t="s">
         <v>5</v>
@@ -4230,81 +4274,81 @@
         <v>6</v>
       </c>
       <c r="H75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C76" t="s">
         <v>282</v>
-      </c>
-      <c r="B76" t="s">
-        <v>218</v>
-      </c>
-      <c r="C76" t="s">
-        <v>283</v>
       </c>
       <c r="D76" t="str">
         <f t="shared" si="1"/>
         <v>4088</v>
       </c>
       <c r="E76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F76" t="s">
+        <v>283</v>
+      </c>
+      <c r="G76" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" t="s">
         <v>284</v>
       </c>
-      <c r="G76" t="s">
-        <v>33</v>
-      </c>
-      <c r="H76" t="s">
-        <v>285</v>
-      </c>
       <c r="I76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" t="s">
         <v>286</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>287</v>
-      </c>
-      <c r="C77" t="s">
-        <v>288</v>
       </c>
       <c r="D77" t="str">
         <f t="shared" si="1"/>
         <v>8574</v>
       </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F77" t="s">
+        <v>288</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s">
         <v>289</v>
       </c>
-      <c r="G77" t="s">
-        <v>33</v>
-      </c>
-      <c r="H77" t="s">
-        <v>290</v>
-      </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
+        <v>290</v>
+      </c>
+      <c r="B78" t="s">
         <v>291</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>292</v>
-      </c>
-      <c r="C78" t="s">
-        <v>293</v>
       </c>
       <c r="D78" t="str">
         <f t="shared" si="1"/>
@@ -4317,10 +4361,10 @@
         <v>5</v>
       </c>
       <c r="G78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I78" t="s">
         <v>8</v>
@@ -4328,13 +4372,13 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
+        <v>294</v>
+      </c>
+      <c r="B79" t="s">
         <v>295</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>296</v>
-      </c>
-      <c r="C79" t="s">
-        <v>297</v>
       </c>
       <c r="D79" t="str">
         <f t="shared" si="1"/>
@@ -4347,24 +4391,24 @@
         <v>5</v>
       </c>
       <c r="G79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
+        <v>297</v>
+      </c>
+      <c r="B80" t="s">
         <v>298</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>299</v>
-      </c>
-      <c r="C80" t="s">
-        <v>300</v>
       </c>
       <c r="D80" t="str">
         <f t="shared" si="1"/>
@@ -4377,54 +4421,54 @@
         <v>5</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
+        <v>300</v>
+      </c>
+      <c r="B81" t="s">
         <v>301</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>302</v>
-      </c>
-      <c r="C81" t="s">
-        <v>303</v>
       </c>
       <c r="D81" t="str">
         <f t="shared" si="1"/>
         <v>1921</v>
       </c>
       <c r="E81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F81" t="s">
+        <v>303</v>
+      </c>
+      <c r="G81" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" t="s">
         <v>304</v>
       </c>
-      <c r="G81" t="s">
-        <v>23</v>
-      </c>
-      <c r="H81" t="s">
-        <v>305</v>
-      </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
+        <v>305</v>
+      </c>
+      <c r="B82" t="s">
         <v>306</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>307</v>
-      </c>
-      <c r="C82" t="s">
-        <v>308</v>
       </c>
       <c r="D82" t="str">
         <f t="shared" si="1"/>
@@ -4434,27 +4478,27 @@
         <v>4</v>
       </c>
       <c r="F82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I82" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
+        <v>309</v>
+      </c>
+      <c r="B83" t="s">
         <v>310</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>311</v>
-      </c>
-      <c r="C83" t="s">
-        <v>312</v>
       </c>
       <c r="D83" t="str">
         <f t="shared" si="1"/>
@@ -4464,13 +4508,13 @@
         <v>4</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I83" t="s">
         <v>8</v>
@@ -4478,43 +4522,43 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
+        <v>313</v>
+      </c>
+      <c r="B84" t="s">
         <v>314</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>315</v>
-      </c>
-      <c r="C84" t="s">
-        <v>316</v>
       </c>
       <c r="D84" t="str">
         <f t="shared" si="1"/>
         <v>0986</v>
       </c>
       <c r="E84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" t="s">
         <v>12</v>
       </c>
-      <c r="F84" t="s">
-        <v>13</v>
-      </c>
       <c r="G84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
+        <v>316</v>
+      </c>
+      <c r="B85" t="s">
         <v>317</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>318</v>
-      </c>
-      <c r="C85" t="s">
-        <v>319</v>
       </c>
       <c r="D85" t="str">
         <f t="shared" si="1"/>
@@ -4524,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="F85" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G85" t="s">
         <v>6</v>
       </c>
       <c r="H85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I85" t="s">
         <v>8</v>
@@ -4538,13 +4582,13 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" t="s">
         <v>189</v>
-      </c>
-      <c r="C86" t="s">
-        <v>190</v>
       </c>
       <c r="D86" t="str">
         <f t="shared" si="1"/>
@@ -4557,10 +4601,10 @@
         <v>5</v>
       </c>
       <c r="G86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I86" t="s">
         <v>8</v>
@@ -4568,13 +4612,13 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B87" t="s">
+        <v>85</v>
+      </c>
+      <c r="C87" t="s">
         <v>86</v>
-      </c>
-      <c r="C87" t="s">
-        <v>87</v>
       </c>
       <c r="D87" t="str">
         <f t="shared" si="1"/>
@@ -4584,13 +4628,13 @@
         <v>4</v>
       </c>
       <c r="F87" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G87" t="s">
         <v>6</v>
       </c>
       <c r="H87" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I87" t="s">
         <v>8</v>
@@ -4598,13 +4642,13 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B88" t="s">
+        <v>215</v>
+      </c>
+      <c r="C88" t="s">
         <v>216</v>
-      </c>
-      <c r="C88" t="s">
-        <v>217</v>
       </c>
       <c r="D88" t="str">
         <f t="shared" si="1"/>
@@ -4614,27 +4658,27 @@
         <v>4</v>
       </c>
       <c r="F88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H88" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
+        <v>323</v>
+      </c>
+      <c r="B89" t="s">
         <v>324</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>325</v>
-      </c>
-      <c r="C89" t="s">
-        <v>326</v>
       </c>
       <c r="D89" t="str">
         <f t="shared" si="1"/>
@@ -4647,24 +4691,24 @@
         <v>5</v>
       </c>
       <c r="G89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
+        <v>326</v>
+      </c>
+      <c r="B90" t="s">
         <v>327</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>328</v>
-      </c>
-      <c r="C90" t="s">
-        <v>329</v>
       </c>
       <c r="D90" t="str">
         <f t="shared" si="1"/>
@@ -4674,27 +4718,27 @@
         <v>4</v>
       </c>
       <c r="F90" t="s">
+        <v>329</v>
+      </c>
+      <c r="G90" t="s">
+        <v>90</v>
+      </c>
+      <c r="H90" t="s">
         <v>330</v>
       </c>
-      <c r="G90" t="s">
-        <v>91</v>
-      </c>
-      <c r="H90" t="s">
-        <v>331</v>
-      </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
+        <v>331</v>
+      </c>
+      <c r="B91" t="s">
         <v>332</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>333</v>
-      </c>
-      <c r="C91" t="s">
-        <v>334</v>
       </c>
       <c r="D91" t="str">
         <f t="shared" si="1"/>
@@ -4704,27 +4748,27 @@
         <v>4</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G91" t="s">
         <v>6</v>
       </c>
       <c r="H91" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
+        <v>335</v>
+      </c>
+      <c r="B92" t="s">
         <v>336</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>337</v>
-      </c>
-      <c r="C92" t="s">
-        <v>338</v>
       </c>
       <c r="D92" t="str">
         <f t="shared" si="1"/>
@@ -4734,57 +4778,57 @@
         <v>4</v>
       </c>
       <c r="F92" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G92" t="s">
         <v>6</v>
       </c>
       <c r="H92" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
+        <v>339</v>
+      </c>
+      <c r="B93" t="s">
         <v>340</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>341</v>
-      </c>
-      <c r="C93" t="s">
-        <v>342</v>
       </c>
       <c r="D93" t="str">
         <f t="shared" si="1"/>
         <v>7662</v>
       </c>
       <c r="E93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G93" t="s">
         <v>6</v>
       </c>
       <c r="H93" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93" t="s">
         <v>18</v>
-      </c>
-      <c r="I93" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
+        <v>343</v>
+      </c>
+      <c r="B94" t="s">
         <v>344</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>345</v>
-      </c>
-      <c r="C94" t="s">
-        <v>346</v>
       </c>
       <c r="D94" t="str">
         <f t="shared" si="1"/>
@@ -4797,10 +4841,10 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I94" t="s">
         <v>8</v>
@@ -4808,13 +4852,13 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
+        <v>347</v>
+      </c>
+      <c r="B95" t="s">
         <v>348</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>349</v>
-      </c>
-      <c r="C95" t="s">
-        <v>350</v>
       </c>
       <c r="D95" t="str">
         <f t="shared" si="1"/>
@@ -4827,24 +4871,24 @@
         <v>5</v>
       </c>
       <c r="G95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I95" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B96" t="s">
+        <v>324</v>
+      </c>
+      <c r="C96" t="s">
         <v>325</v>
-      </c>
-      <c r="C96" t="s">
-        <v>326</v>
       </c>
       <c r="D96" t="str">
         <f t="shared" si="1"/>
@@ -4857,24 +4901,24 @@
         <v>5</v>
       </c>
       <c r="G96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
+        <v>352</v>
+      </c>
+      <c r="B97" t="s">
         <v>353</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>354</v>
-      </c>
-      <c r="C97" t="s">
-        <v>355</v>
       </c>
       <c r="D97" t="str">
         <f t="shared" si="1"/>
@@ -4884,57 +4928,57 @@
         <v>4</v>
       </c>
       <c r="F97" t="s">
+        <v>355</v>
+      </c>
+      <c r="G97" t="s">
+        <v>90</v>
+      </c>
+      <c r="H97" t="s">
         <v>356</v>
       </c>
-      <c r="G97" t="s">
-        <v>91</v>
-      </c>
-      <c r="H97" t="s">
-        <v>357</v>
-      </c>
       <c r="I97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
+        <v>357</v>
+      </c>
+      <c r="B98" t="s">
         <v>358</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>359</v>
-      </c>
-      <c r="C98" t="s">
-        <v>360</v>
       </c>
       <c r="D98" t="str">
         <f t="shared" si="1"/>
         <v>4671</v>
       </c>
       <c r="E98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>5</v>
       </c>
       <c r="G98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H98" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
+        <v>361</v>
+      </c>
+      <c r="B99" t="s">
         <v>362</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>363</v>
-      </c>
-      <c r="C99" t="s">
-        <v>364</v>
       </c>
       <c r="D99" t="str">
         <f t="shared" si="1"/>
@@ -4947,10 +4991,10 @@
         <v>5</v>
       </c>
       <c r="G99" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I99" t="s">
         <v>8</v>
@@ -4958,13 +5002,13 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
+        <v>365</v>
+      </c>
+      <c r="B100" t="s">
         <v>366</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>367</v>
-      </c>
-      <c r="C100" t="s">
-        <v>368</v>
       </c>
       <c r="D100" t="str">
         <f t="shared" si="1"/>
@@ -4977,24 +5021,24 @@
         <v>5</v>
       </c>
       <c r="G100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I100" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
+        <v>368</v>
+      </c>
+      <c r="B101" t="s">
         <v>369</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>370</v>
-      </c>
-      <c r="C101" t="s">
-        <v>371</v>
       </c>
       <c r="D101" t="str">
         <f t="shared" si="1"/>
@@ -5007,10 +5051,10 @@
         <v>5</v>
       </c>
       <c r="G101" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I101" t="s">
         <v>8</v>
@@ -5018,13 +5062,13 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
+        <v>371</v>
+      </c>
+      <c r="B102" t="s">
         <v>372</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>373</v>
-      </c>
-      <c r="C102" t="s">
-        <v>374</v>
       </c>
       <c r="D102" t="str">
         <f t="shared" si="1"/>
@@ -5034,34 +5078,34 @@
         <v>4</v>
       </c>
       <c r="F102" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
+        <v>375</v>
+      </c>
+      <c r="B103" t="s">
         <v>376</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>377</v>
-      </c>
-      <c r="C103" t="s">
-        <v>378</v>
       </c>
       <c r="D103" t="str">
         <f t="shared" si="1"/>
         <v>8751</v>
       </c>
       <c r="E103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F103" t="s">
         <v>5</v>
@@ -5070,51 +5114,51 @@
         <v>6</v>
       </c>
       <c r="H103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B104" t="s">
         <v>379</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>380</v>
-      </c>
-      <c r="C104" t="s">
-        <v>381</v>
       </c>
       <c r="D104" t="str">
         <f t="shared" si="1"/>
         <v>8318</v>
       </c>
       <c r="E104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F104" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G104" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
+        <v>382</v>
+      </c>
+      <c r="B105" t="s">
         <v>383</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>384</v>
-      </c>
-      <c r="C105" t="s">
-        <v>385</v>
       </c>
       <c r="D105" t="str">
         <f t="shared" si="1"/>
@@ -5127,10 +5171,10 @@
         <v>5</v>
       </c>
       <c r="G105" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I105" t="s">
         <v>8</v>
@@ -5138,13 +5182,13 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
+        <v>385</v>
+      </c>
+      <c r="B106" t="s">
         <v>386</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>387</v>
-      </c>
-      <c r="C106" t="s">
-        <v>388</v>
       </c>
       <c r="D106" t="str">
         <f t="shared" si="1"/>
@@ -5154,27 +5198,27 @@
         <v>4</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I106" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
+        <v>388</v>
+      </c>
+      <c r="B107" t="s">
         <v>389</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>390</v>
-      </c>
-      <c r="C107" t="s">
-        <v>391</v>
       </c>
       <c r="D107" t="str">
         <f t="shared" si="1"/>
@@ -5187,24 +5231,24 @@
         <v>5</v>
       </c>
       <c r="G107" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
+        <v>392</v>
+      </c>
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" t="s">
         <v>393</v>
-      </c>
-      <c r="B108" t="s">
-        <v>28</v>
-      </c>
-      <c r="C108" t="s">
-        <v>394</v>
       </c>
       <c r="D108" t="str">
         <f t="shared" si="1"/>
@@ -5217,10 +5261,10 @@
         <v>5</v>
       </c>
       <c r="G108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I108" t="s">
         <v>8</v>
@@ -5228,13 +5272,13 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
+        <v>394</v>
+      </c>
+      <c r="B109" t="s">
         <v>395</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>396</v>
-      </c>
-      <c r="C109" t="s">
-        <v>397</v>
       </c>
       <c r="D109" t="str">
         <f t="shared" si="1"/>
@@ -5244,13 +5288,13 @@
         <v>4</v>
       </c>
       <c r="F109" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H109" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -5258,13 +5302,13 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
+        <v>398</v>
+      </c>
+      <c r="B110" t="s">
         <v>399</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>400</v>
-      </c>
-      <c r="C110" t="s">
-        <v>401</v>
       </c>
       <c r="D110" t="str">
         <f t="shared" si="1"/>
@@ -5274,13 +5318,13 @@
         <v>4</v>
       </c>
       <c r="F110" t="s">
+        <v>401</v>
+      </c>
+      <c r="G110" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" t="s">
         <v>402</v>
-      </c>
-      <c r="G110" t="s">
-        <v>23</v>
-      </c>
-      <c r="H110" t="s">
-        <v>403</v>
       </c>
       <c r="I110" t="s">
         <v>8</v>
@@ -5288,13 +5332,13 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
+        <v>403</v>
+      </c>
+      <c r="B111" t="s">
         <v>404</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>405</v>
-      </c>
-      <c r="C111" t="s">
-        <v>406</v>
       </c>
       <c r="D111" t="str">
         <f t="shared" si="1"/>
@@ -5307,24 +5351,24 @@
         <v>5</v>
       </c>
       <c r="G111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I111" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
+        <v>406</v>
+      </c>
+      <c r="B112" t="s">
         <v>407</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>408</v>
-      </c>
-      <c r="C112" t="s">
-        <v>409</v>
       </c>
       <c r="D112" t="str">
         <f t="shared" si="1"/>
@@ -5334,27 +5378,27 @@
         <v>4</v>
       </c>
       <c r="F112" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G112" t="s">
         <v>6</v>
       </c>
       <c r="H112" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I112" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
+        <v>410</v>
+      </c>
+      <c r="B113" t="s">
         <v>411</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>412</v>
-      </c>
-      <c r="C113" t="s">
-        <v>413</v>
       </c>
       <c r="D113" t="str">
         <f t="shared" si="1"/>
@@ -5367,24 +5411,24 @@
         <v>5</v>
       </c>
       <c r="G113" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
+        <v>415</v>
+      </c>
+      <c r="B114" t="s">
         <v>416</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>417</v>
-      </c>
-      <c r="C114" t="s">
-        <v>418</v>
       </c>
       <c r="D114" t="str">
         <f t="shared" si="1"/>
@@ -5394,27 +5438,27 @@
         <v>4</v>
       </c>
       <c r="F114" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G114" t="s">
         <v>6</v>
       </c>
       <c r="H114" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I114" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
+        <v>419</v>
+      </c>
+      <c r="B115" t="s">
         <v>420</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>421</v>
-      </c>
-      <c r="C115" t="s">
-        <v>422</v>
       </c>
       <c r="D115" t="str">
         <f t="shared" si="1"/>
@@ -5424,13 +5468,13 @@
         <v>4</v>
       </c>
       <c r="F115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G115" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -5438,13 +5482,13 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B116" t="s">
+        <v>181</v>
+      </c>
+      <c r="C116" t="s">
         <v>182</v>
-      </c>
-      <c r="C116" t="s">
-        <v>183</v>
       </c>
       <c r="D116" t="str">
         <f t="shared" si="1"/>
@@ -5457,24 +5501,24 @@
         <v>5</v>
       </c>
       <c r="G116" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H116" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I116" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
+        <v>424</v>
+      </c>
+      <c r="B117" t="s">
+        <v>244</v>
+      </c>
+      <c r="C117" t="s">
         <v>425</v>
-      </c>
-      <c r="B117" t="s">
-        <v>245</v>
-      </c>
-      <c r="C117" t="s">
-        <v>426</v>
       </c>
       <c r="D117" t="str">
         <f t="shared" si="1"/>
@@ -5487,10 +5531,10 @@
         <v>5</v>
       </c>
       <c r="G117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H117" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I117" t="s">
         <v>8</v>
@@ -5498,13 +5542,13 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
+        <v>426</v>
+      </c>
+      <c r="B118" t="s">
         <v>427</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>428</v>
-      </c>
-      <c r="C118" t="s">
-        <v>429</v>
       </c>
       <c r="D118" t="str">
         <f t="shared" si="1"/>
@@ -5514,13 +5558,13 @@
         <v>4</v>
       </c>
       <c r="F118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G118" t="s">
         <v>6</v>
       </c>
       <c r="H118" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I118" t="s">
         <v>8</v>
@@ -5528,13 +5572,13 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B119" t="s">
+        <v>404</v>
+      </c>
+      <c r="C119" t="s">
         <v>405</v>
-      </c>
-      <c r="C119" t="s">
-        <v>406</v>
       </c>
       <c r="D119" t="str">
         <f t="shared" si="1"/>
@@ -5544,57 +5588,57 @@
         <v>4</v>
       </c>
       <c r="F119" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I119" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
+        <v>431</v>
+      </c>
+      <c r="B120" t="s">
         <v>432</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>433</v>
-      </c>
-      <c r="C120" t="s">
-        <v>434</v>
       </c>
       <c r="D120" t="str">
         <f t="shared" si="1"/>
         <v>4269</v>
       </c>
       <c r="E120" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" t="s">
         <v>12</v>
       </c>
-      <c r="F120" t="s">
-        <v>13</v>
-      </c>
       <c r="G120" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
+        <v>434</v>
+      </c>
+      <c r="B121" t="s">
         <v>435</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>436</v>
-      </c>
-      <c r="C121" t="s">
-        <v>437</v>
       </c>
       <c r="D121" t="str">
         <f t="shared" si="1"/>
@@ -5604,13 +5648,13 @@
         <v>4</v>
       </c>
       <c r="F121" t="s">
+        <v>437</v>
+      </c>
+      <c r="G121" t="s">
+        <v>22</v>
+      </c>
+      <c r="H121" t="s">
         <v>438</v>
-      </c>
-      <c r="G121" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" t="s">
-        <v>439</v>
       </c>
       <c r="I121" t="s">
         <v>8</v>
@@ -5618,13 +5662,13 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
+        <v>439</v>
+      </c>
+      <c r="B122" t="s">
         <v>440</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>441</v>
-      </c>
-      <c r="C122" t="s">
-        <v>442</v>
       </c>
       <c r="D122" t="str">
         <f t="shared" si="1"/>
@@ -5640,7 +5684,7 @@
         <v>6</v>
       </c>
       <c r="H122" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I122" t="s">
         <v>8</v>
@@ -5648,13 +5692,13 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
+        <v>443</v>
+      </c>
+      <c r="B123" t="s">
         <v>444</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>445</v>
-      </c>
-      <c r="C123" t="s">
-        <v>446</v>
       </c>
       <c r="D123" t="str">
         <f t="shared" si="1"/>
@@ -5664,13 +5708,13 @@
         <v>4</v>
       </c>
       <c r="F123" t="s">
+        <v>446</v>
+      </c>
+      <c r="G123" t="s">
+        <v>6</v>
+      </c>
+      <c r="H123" t="s">
         <v>447</v>
-      </c>
-      <c r="G123" t="s">
-        <v>6</v>
-      </c>
-      <c r="H123" t="s">
-        <v>448</v>
       </c>
       <c r="I123" t="s">
         <v>8</v>
@@ -5678,13 +5722,13 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
+        <v>448</v>
+      </c>
+      <c r="B124" t="s">
         <v>449</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>450</v>
-      </c>
-      <c r="C124" t="s">
-        <v>451</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="1"/>
@@ -5694,27 +5738,27 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G124" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I124" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
+        <v>451</v>
+      </c>
+      <c r="B125" t="s">
         <v>452</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>453</v>
-      </c>
-      <c r="C125" t="s">
-        <v>454</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="1"/>
@@ -5730,28 +5774,28 @@
         <v>6</v>
       </c>
       <c r="H125" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I125" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B126" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="1"/>
         <v>3852</v>
       </c>
       <c r="E126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F126" t="s">
         <v>5</v>
@@ -5760,21 +5804,21 @@
         <v>6</v>
       </c>
       <c r="H126" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I126" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
+        <v>455</v>
+      </c>
+      <c r="B127" t="s">
         <v>456</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>457</v>
-      </c>
-      <c r="C127" t="s">
-        <v>458</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="1"/>
@@ -5784,7 +5828,7 @@
         <v>4</v>
       </c>
       <c r="F127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127" t="s">
         <v>6</v>
@@ -5793,18 +5837,18 @@
         <v>7</v>
       </c>
       <c r="I127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
+        <v>458</v>
+      </c>
+      <c r="B128" t="s">
         <v>459</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>460</v>
-      </c>
-      <c r="C128" t="s">
-        <v>461</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="1"/>
@@ -5817,24 +5861,24 @@
         <v>5</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H128" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I128" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
+        <v>462</v>
+      </c>
+      <c r="B129" t="s">
         <v>463</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>464</v>
-      </c>
-      <c r="C129" t="s">
-        <v>465</v>
       </c>
       <c r="D129" t="str">
         <f t="shared" si="1"/>
@@ -5847,24 +5891,24 @@
         <v>5</v>
       </c>
       <c r="G129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H129" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
+        <v>465</v>
+      </c>
+      <c r="B130" t="s">
         <v>466</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>467</v>
-      </c>
-      <c r="C130" t="s">
-        <v>468</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="1"/>
@@ -5877,10 +5921,10 @@
         <v>5</v>
       </c>
       <c r="G130" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H130" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I130" t="s">
         <v>8</v>
@@ -5888,20 +5932,20 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B131" t="s">
+        <v>141</v>
+      </c>
+      <c r="C131" t="s">
         <v>142</v>
-      </c>
-      <c r="C131" t="s">
-        <v>143</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="1"/>
         <v>2842</v>
       </c>
       <c r="E131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F131" t="s">
         <v>5</v>
@@ -5910,51 +5954,51 @@
         <v>6</v>
       </c>
       <c r="H131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I131" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
+        <v>469</v>
+      </c>
+      <c r="B132" t="s">
         <v>470</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>471</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="str">
+        <f t="shared" ref="D132:D152" si="2">RIGHT(C132, 4)</f>
+        <v>8109</v>
+      </c>
+      <c r="E132" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" t="s">
+        <v>5</v>
+      </c>
+      <c r="G132" t="s">
+        <v>22</v>
+      </c>
+      <c r="H132" t="s">
         <v>472</v>
       </c>
-      <c r="D132" t="str">
-        <f t="shared" ref="D132:D146" si="2">RIGHT(C132, 4)</f>
-        <v>8109</v>
-      </c>
-      <c r="E132" t="s">
-        <v>4</v>
-      </c>
-      <c r="F132" t="s">
-        <v>5</v>
-      </c>
-      <c r="G132" t="s">
-        <v>23</v>
-      </c>
-      <c r="H132" t="s">
-        <v>473</v>
-      </c>
       <c r="I132" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
+        <v>473</v>
+      </c>
+      <c r="B133" t="s">
         <v>474</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>475</v>
-      </c>
-      <c r="C133" t="s">
-        <v>476</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="2"/>
@@ -5964,27 +6008,27 @@
         <v>4</v>
       </c>
       <c r="F133" t="s">
+        <v>476</v>
+      </c>
+      <c r="G133" t="s">
+        <v>6</v>
+      </c>
+      <c r="H133" t="s">
         <v>477</v>
       </c>
-      <c r="G133" t="s">
-        <v>6</v>
-      </c>
-      <c r="H133" t="s">
-        <v>478</v>
-      </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
+        <v>478</v>
+      </c>
+      <c r="B134" t="s">
         <v>479</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>480</v>
-      </c>
-      <c r="C134" t="s">
-        <v>481</v>
       </c>
       <c r="D134" t="str">
         <f t="shared" si="2"/>
@@ -5994,27 +6038,27 @@
         <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G134" t="s">
         <v>6</v>
       </c>
       <c r="H134" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I134" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
+        <v>482</v>
+      </c>
+      <c r="B135" t="s">
         <v>483</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>484</v>
-      </c>
-      <c r="C135" t="s">
-        <v>485</v>
       </c>
       <c r="D135" t="str">
         <f t="shared" si="2"/>
@@ -6024,43 +6068,43 @@
         <v>4</v>
       </c>
       <c r="F135" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G135" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
+        <v>485</v>
+      </c>
+      <c r="B136" t="s">
         <v>486</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>487</v>
-      </c>
-      <c r="C136" t="s">
-        <v>488</v>
       </c>
       <c r="D136" t="str">
         <f t="shared" si="2"/>
         <v>6704</v>
       </c>
       <c r="E136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F136" t="s">
         <v>5</v>
       </c>
       <c r="G136" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I136" t="s">
         <v>8</v>
@@ -6068,29 +6112,29 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
+        <v>489</v>
+      </c>
+      <c r="B137" t="s">
         <v>490</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>491</v>
-      </c>
-      <c r="C137" t="s">
-        <v>492</v>
       </c>
       <c r="D137" t="str">
         <f t="shared" si="2"/>
         <v>0108</v>
       </c>
       <c r="E137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F137" t="s">
         <v>5</v>
       </c>
       <c r="G137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H137" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I137" t="s">
         <v>8</v>
@@ -6098,20 +6142,20 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
+        <v>492</v>
+      </c>
+      <c r="B138" t="s">
         <v>493</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>494</v>
-      </c>
-      <c r="C138" t="s">
-        <v>495</v>
       </c>
       <c r="D138" t="str">
         <f t="shared" si="2"/>
         <v>1204</v>
       </c>
       <c r="E138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>5</v>
@@ -6120,7 +6164,7 @@
         <v>6</v>
       </c>
       <c r="H138" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I138" t="s">
         <v>8</v>
@@ -6128,13 +6172,13 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
+        <v>496</v>
+      </c>
+      <c r="B139" t="s">
         <v>497</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>498</v>
-      </c>
-      <c r="C139" t="s">
-        <v>499</v>
       </c>
       <c r="D139" t="str">
         <f t="shared" si="2"/>
@@ -6144,13 +6188,13 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G139" t="s">
         <v>6</v>
       </c>
       <c r="H139" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I139" t="s">
         <v>8</v>
@@ -6158,13 +6202,13 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
+        <v>500</v>
+      </c>
+      <c r="B140" t="s">
         <v>501</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>502</v>
-      </c>
-      <c r="C140" t="s">
-        <v>503</v>
       </c>
       <c r="D140" t="str">
         <f t="shared" si="2"/>
@@ -6174,57 +6218,57 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G140" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H140" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I140" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
+        <v>504</v>
+      </c>
+      <c r="B141" t="s">
         <v>505</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>506</v>
-      </c>
-      <c r="C141" t="s">
-        <v>507</v>
       </c>
       <c r="D141" t="str">
         <f t="shared" si="2"/>
         <v>0790</v>
       </c>
       <c r="E141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F141" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G141" t="s">
         <v>6</v>
       </c>
       <c r="H141" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I141" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
+        <v>508</v>
+      </c>
+      <c r="B142" t="s">
         <v>509</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>510</v>
-      </c>
-      <c r="C142" t="s">
-        <v>511</v>
       </c>
       <c r="D142" t="str">
         <f t="shared" si="2"/>
@@ -6248,13 +6292,13 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
+        <v>511</v>
+      </c>
+      <c r="B143" t="s">
         <v>512</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>513</v>
-      </c>
-      <c r="C143" t="s">
-        <v>514</v>
       </c>
       <c r="D143" t="str">
         <f t="shared" si="2"/>
@@ -6267,10 +6311,10 @@
         <v>5</v>
       </c>
       <c r="G143" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H143" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I143" t="s">
         <v>8</v>
@@ -6278,13 +6322,13 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
+        <v>515</v>
+      </c>
+      <c r="B144" t="s">
         <v>516</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>517</v>
-      </c>
-      <c r="C144" t="s">
-        <v>518</v>
       </c>
       <c r="D144" t="str">
         <f t="shared" si="2"/>
@@ -6303,18 +6347,18 @@
         <v>7</v>
       </c>
       <c r="I144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
+        <v>518</v>
+      </c>
+      <c r="B145" t="s">
         <v>519</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>520</v>
-      </c>
-      <c r="C145" t="s">
-        <v>521</v>
       </c>
       <c r="D145" t="str">
         <f t="shared" si="2"/>
@@ -6324,45 +6368,225 @@
         <v>4</v>
       </c>
       <c r="F145" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G145" t="s">
         <v>6</v>
       </c>
       <c r="H145" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B146" t="s">
+        <v>175</v>
+      </c>
+      <c r="C146" t="s">
         <v>176</v>
-      </c>
-      <c r="C146" t="s">
-        <v>177</v>
       </c>
       <c r="D146" t="str">
         <f t="shared" si="2"/>
         <v>1118</v>
       </c>
       <c r="E146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F146" t="s">
+        <v>66</v>
+      </c>
+      <c r="G146" t="s">
+        <v>32</v>
+      </c>
+      <c r="H146" t="s">
+        <v>523</v>
+      </c>
+      <c r="I146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>508</v>
+      </c>
+      <c r="B147" t="s">
+        <v>534</v>
+      </c>
+      <c r="C147">
+        <v>1050161454</v>
+      </c>
+      <c r="D147" t="str">
+        <f t="shared" si="2"/>
+        <v>1454</v>
+      </c>
+      <c r="E147" t="s">
+        <v>544</v>
+      </c>
+      <c r="F147" t="s">
+        <v>543</v>
+      </c>
+      <c r="G147" t="s">
+        <v>32</v>
+      </c>
+      <c r="H147" t="s">
+        <v>461</v>
+      </c>
+      <c r="I147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>511</v>
+      </c>
+      <c r="B148" t="s">
+        <v>535</v>
+      </c>
+      <c r="C148">
+        <v>1022162592</v>
+      </c>
+      <c r="D148" t="str">
+        <f t="shared" si="2"/>
+        <v>2592</v>
+      </c>
+      <c r="E148" t="s">
+        <v>540</v>
+      </c>
+      <c r="F148" t="s">
+        <v>543</v>
+      </c>
+      <c r="G148" t="s">
+        <v>22</v>
+      </c>
+      <c r="H148" t="s">
         <v>67</v>
       </c>
-      <c r="G146" t="s">
-        <v>33</v>
-      </c>
-      <c r="H146" t="s">
-        <v>524</v>
-      </c>
-      <c r="I146" t="s">
+      <c r="I148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>515</v>
+      </c>
+      <c r="B149" t="s">
+        <v>536</v>
+      </c>
+      <c r="C149">
+        <v>1090399733</v>
+      </c>
+      <c r="D149" t="str">
+        <f t="shared" si="2"/>
+        <v>9733</v>
+      </c>
+      <c r="E149" t="s">
+        <v>541</v>
+      </c>
+      <c r="F149" t="s">
+        <v>542</v>
+      </c>
+      <c r="G149" t="s">
+        <v>22</v>
+      </c>
+      <c r="H149" t="s">
+        <v>53</v>
+      </c>
+      <c r="I149" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>518</v>
+      </c>
+      <c r="B150" t="s">
+        <v>537</v>
+      </c>
+      <c r="C150">
+        <v>1029469622</v>
+      </c>
+      <c r="D150" t="str">
+        <f t="shared" si="2"/>
+        <v>9622</v>
+      </c>
+      <c r="E150" t="s">
+        <v>540</v>
+      </c>
+      <c r="F150" t="s">
+        <v>542</v>
+      </c>
+      <c r="G150" t="s">
+        <v>6</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>522</v>
+      </c>
+      <c r="B151" t="s">
+        <v>538</v>
+      </c>
+      <c r="C151">
+        <v>1050031027</v>
+      </c>
+      <c r="D151" t="str">
+        <f t="shared" si="2"/>
+        <v>1027</v>
+      </c>
+      <c r="E151" t="s">
+        <v>540</v>
+      </c>
+      <c r="F151" t="s">
+        <v>542</v>
+      </c>
+      <c r="G151" t="s">
+        <v>22</v>
+      </c>
+      <c r="H151" t="s">
+        <v>472</v>
+      </c>
+      <c r="I151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>518</v>
+      </c>
+      <c r="B152" t="s">
+        <v>539</v>
+      </c>
+      <c r="C152">
+        <v>1032617715</v>
+      </c>
+      <c r="D152" t="str">
+        <f t="shared" si="2"/>
+        <v>7715</v>
+      </c>
+      <c r="E152" t="s">
+        <v>540</v>
+      </c>
+      <c r="F152" t="s">
+        <v>542</v>
+      </c>
+      <c r="G152" t="s">
+        <v>6</v>
+      </c>
+      <c r="H152" t="s">
+        <v>477</v>
+      </c>
+      <c r="I152" t="s">
         <v>8</v>
       </c>
     </row>

--- a/entry_list.xlsx
+++ b/entry_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="615">
   <si>
     <t>연락처 (*정확히 기재)(*)</t>
   </si>
@@ -1862,6 +1862,18 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>3시간 40분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3시간 10분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7159,8 +7171,8 @@
       <c r="G164" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H164" s="5">
-        <v>0.15277777777777776</v>
+      <c r="H164" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="I164" s="4" t="s">
         <v>608</v>
@@ -7186,8 +7198,8 @@
       <c r="G165" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H165" s="5">
-        <v>0.16666666666666666</v>
+      <c r="H165" s="5" t="s">
+        <v>613</v>
       </c>
       <c r="I165" s="4" t="s">
         <v>609</v>
@@ -7213,8 +7225,8 @@
       <c r="G166" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H166" s="5">
-        <v>0.16666666666666666</v>
+      <c r="H166" s="5" t="s">
+        <v>613</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>609</v>
@@ -7240,8 +7252,8 @@
       <c r="G167" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H167" s="5">
-        <v>0.13194444444444445</v>
+      <c r="H167" s="5" t="s">
+        <v>614</v>
       </c>
       <c r="I167" s="4" t="s">
         <v>610</v>
@@ -7267,8 +7279,8 @@
       <c r="G168" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H168" s="5">
-        <v>0.16666666666666666</v>
+      <c r="H168" s="5" t="s">
+        <v>613</v>
       </c>
       <c r="I168" s="4" t="s">
         <v>609</v>
@@ -7294,8 +7306,8 @@
       <c r="G169" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="H169" s="5">
-        <v>0.15277777777777779</v>
+      <c r="H169" s="5" t="s">
+        <v>612</v>
       </c>
       <c r="I169" s="4" t="s">
         <v>611</v>

--- a/entry_list.xlsx
+++ b/entry_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="617">
   <si>
     <t>연락처 (*정확히 기재)(*)</t>
   </si>
@@ -1873,6 +1873,13 @@
   </si>
   <si>
     <t>3시간 10분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단체접수 6명</t>
+  </si>
+  <si>
+    <t>단체접수 6명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7152,6 +7159,9 @@
       </c>
     </row>
     <row r="164" spans="1:9">
+      <c r="A164" s="1" t="s">
+        <v>616</v>
+      </c>
       <c r="B164" s="3" t="s">
         <v>594</v>
       </c>
@@ -7179,6 +7189,9 @@
       </c>
     </row>
     <row r="165" spans="1:9">
+      <c r="A165" s="1" t="s">
+        <v>616</v>
+      </c>
       <c r="B165" s="3" t="s">
         <v>595</v>
       </c>
@@ -7206,6 +7219,9 @@
       </c>
     </row>
     <row r="166" spans="1:9">
+      <c r="A166" s="1" t="s">
+        <v>615</v>
+      </c>
       <c r="B166" s="3" t="s">
         <v>596</v>
       </c>
@@ -7233,6 +7249,9 @@
       </c>
     </row>
     <row r="167" spans="1:9">
+      <c r="A167" s="1" t="s">
+        <v>615</v>
+      </c>
       <c r="B167" s="3" t="s">
         <v>597</v>
       </c>
@@ -7260,6 +7279,9 @@
       </c>
     </row>
     <row r="168" spans="1:9">
+      <c r="A168" s="1" t="s">
+        <v>615</v>
+      </c>
       <c r="B168" s="3" t="s">
         <v>598</v>
       </c>
@@ -7287,6 +7309,9 @@
       </c>
     </row>
     <row r="169" spans="1:9">
+      <c r="A169" s="1" t="s">
+        <v>615</v>
+      </c>
       <c r="B169" s="3" t="s">
         <v>599</v>
       </c>

--- a/entry_list.xlsx
+++ b/entry_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="623">
   <si>
     <t>연락처 (*정확히 기재)(*)</t>
   </si>
@@ -1880,6 +1880,30 @@
   </si>
   <si>
     <t>단체접수 6명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍길동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍 길 동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3km</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자만한놈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2257,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.75" style="1" customWidth="1"/>
@@ -6209,7 +6233,7 @@
         <v>460</v>
       </c>
       <c r="D132" s="1" t="str">
-        <f t="shared" ref="D132:D169" si="2">RIGHT(C132, 4)</f>
+        <f t="shared" ref="D132:D171" si="2">RIGHT(C132, 4)</f>
         <v>8109</v>
       </c>
       <c r="E132" s="1" t="s">
@@ -7336,6 +7360,60 @@
       </c>
       <c r="I169" s="4" t="s">
         <v>611</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="B170" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C170" s="1">
+        <v>1032617715</v>
+      </c>
+      <c r="D170" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>7715</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H170" s="1">
+        <v>4</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="B171" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1032617715</v>
+      </c>
+      <c r="D171" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>7715</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H171" s="1">
+        <v>4</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/entry_list.xlsx
+++ b/entry_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="728">
   <si>
     <t>연락처 (*정확히 기재)(*)</t>
   </si>
@@ -2203,6 +2203,26 @@
   </si>
   <si>
     <t>01032264082</t>
+  </si>
+  <si>
+    <t>참가비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1시간30분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>납입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미납</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2238,7 +2258,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2248,6 +2268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2266,7 +2292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2285,11 +2311,55 @@
     <xf numFmtId="21" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -2579,20 +2649,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="21.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="1" customWidth="1"/>
-    <col min="7" max="9" width="23.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="1" hidden="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -2620,8 +2692,11 @@
       <c r="I1" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>498</v>
       </c>
@@ -2649,8 +2724,11 @@
       <c r="I2" s="2" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>595</v>
       </c>
@@ -2679,8 +2757,11 @@
       <c r="I3" s="4" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>595</v>
       </c>
@@ -2709,8 +2790,11 @@
       <c r="I4" s="4" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>594</v>
       </c>
@@ -2739,8 +2823,11 @@
       <c r="I5" s="4" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>594</v>
       </c>
@@ -2769,8 +2856,11 @@
       <c r="I6" s="4" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>594</v>
       </c>
@@ -2799,8 +2889,11 @@
       <c r="I7" s="4" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>594</v>
       </c>
@@ -2829,8 +2922,11 @@
       <c r="I8" s="4" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="B9" s="1" t="s">
         <v>596</v>
       </c>
@@ -2850,14 +2946,17 @@
       <c r="G9" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="H9" s="1">
-        <v>4</v>
+      <c r="H9" s="1" t="s">
+        <v>725</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -2886,8 +2985,14 @@
       <c r="I10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>499</v>
       </c>
@@ -2916,8 +3021,14 @@
       <c r="I11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2946,8 +3057,14 @@
       <c r="I12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -2976,8 +3093,14 @@
       <c r="I13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>501</v>
       </c>
@@ -3006,8 +3129,14 @@
       <c r="I14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -3031,13 +3160,19 @@
         <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>724</v>
       </c>
       <c r="I15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -3066,8 +3201,14 @@
       <c r="I16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3096,8 +3237,14 @@
       <c r="I17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3126,8 +3273,14 @@
       <c r="I18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3156,8 +3309,14 @@
       <c r="I19" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>600</v>
       </c>
@@ -3186,8 +3345,14 @@
       <c r="I20" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -3216,8 +3381,14 @@
       <c r="I21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>601</v>
       </c>
@@ -3246,8 +3417,14 @@
       <c r="I22" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>603</v>
       </c>
@@ -3276,8 +3453,14 @@
       <c r="I23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -3306,8 +3489,14 @@
       <c r="I24" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -3336,8 +3525,14 @@
       <c r="I25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -3366,8 +3561,14 @@
       <c r="I26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -3396,8 +3597,14 @@
       <c r="I27" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3426,8 +3633,14 @@
       <c r="I28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -3456,8 +3669,14 @@
       <c r="I29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -3486,8 +3705,14 @@
       <c r="I30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -3516,8 +3741,14 @@
       <c r="I31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -3546,8 +3777,14 @@
       <c r="I32" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -3576,8 +3813,14 @@
       <c r="I33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>100</v>
       </c>
@@ -3606,8 +3849,14 @@
       <c r="I34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
         <v>103</v>
       </c>
@@ -3636,8 +3885,14 @@
       <c r="I35" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -3666,8 +3921,14 @@
       <c r="I36" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -3696,8 +3957,14 @@
       <c r="I37" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
         <v>115</v>
       </c>
@@ -3726,8 +3993,14 @@
       <c r="I38" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -3756,8 +4029,14 @@
       <c r="I39" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>125</v>
       </c>
@@ -3786,8 +4065,14 @@
       <c r="I40" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>129</v>
       </c>
@@ -3816,8 +4101,14 @@
       <c r="I41" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>132</v>
       </c>
@@ -3846,8 +4137,14 @@
       <c r="I42" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>138</v>
       </c>
@@ -3876,8 +4173,14 @@
       <c r="I43" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -3906,8 +4209,14 @@
       <c r="I44" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -3936,8 +4245,14 @@
       <c r="I45" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -3966,8 +4281,14 @@
       <c r="I46" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K46" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>153</v>
       </c>
@@ -3996,8 +4317,14 @@
       <c r="I47" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>157</v>
       </c>
@@ -4026,8 +4353,14 @@
       <c r="I48" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>161</v>
       </c>
@@ -4056,8 +4389,14 @@
       <c r="I49" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="J49" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
         <v>165</v>
       </c>
@@ -4086,8 +4425,14 @@
       <c r="I50" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="J50" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
         <v>604</v>
       </c>
@@ -4116,8 +4461,14 @@
       <c r="I51" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="J51" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>175</v>
       </c>
@@ -4146,8 +4497,14 @@
       <c r="I52" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="J52" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>502</v>
       </c>
@@ -4176,8 +4533,14 @@
       <c r="I53" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="J53" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>180</v>
       </c>
@@ -4206,8 +4569,14 @@
       <c r="I54" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="J54" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>188</v>
       </c>
@@ -4236,8 +4605,14 @@
       <c r="I55" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
         <v>192</v>
       </c>
@@ -4266,8 +4641,14 @@
       <c r="I56" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="J56" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>192</v>
       </c>
@@ -4296,8 +4677,14 @@
       <c r="I57" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="1:9">
+      <c r="J57" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K57" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>503</v>
       </c>
@@ -4326,8 +4713,14 @@
       <c r="I58" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="1:9">
+      <c r="J58" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
         <v>200</v>
       </c>
@@ -4356,8 +4749,14 @@
       <c r="I59" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="60" spans="1:9">
+      <c r="J59" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K59" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>207</v>
       </c>
@@ -4386,8 +4785,14 @@
       <c r="I60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="J60" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>606</v>
       </c>
@@ -4416,8 +4821,14 @@
       <c r="I61" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="J61" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
         <v>213</v>
       </c>
@@ -4446,8 +4857,14 @@
       <c r="I62" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="J62" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
         <v>607</v>
       </c>
@@ -4476,8 +4893,14 @@
       <c r="I63" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="1:9">
+      <c r="J63" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
         <v>218</v>
       </c>
@@ -4506,8 +4929,14 @@
       <c r="I64" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="J64" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
         <v>221</v>
       </c>
@@ -4536,8 +4965,14 @@
       <c r="I65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="J65" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>226</v>
       </c>
@@ -4566,8 +5001,14 @@
       <c r="I66" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="67" spans="1:9">
+      <c r="J66" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
         <v>609</v>
       </c>
@@ -4596,8 +5037,14 @@
       <c r="I67" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="J67" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>234</v>
       </c>
@@ -4626,8 +5073,14 @@
       <c r="I68" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="J68" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -4656,8 +5109,14 @@
       <c r="I69" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>241</v>
       </c>
@@ -4686,8 +5145,14 @@
       <c r="I70" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="71" spans="1:9">
+      <c r="J70" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
         <v>245</v>
       </c>
@@ -4716,8 +5181,14 @@
       <c r="I71" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="J71" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" t="s">
         <v>248</v>
       </c>
@@ -4746,8 +5217,14 @@
       <c r="I72" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="J72" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
         <v>252</v>
       </c>
@@ -4776,8 +5253,14 @@
       <c r="I73" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="J73" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>610</v>
       </c>
@@ -4806,8 +5289,14 @@
       <c r="I74" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="75" spans="1:9">
+      <c r="J74" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K74" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>612</v>
       </c>
@@ -4836,8 +5325,14 @@
       <c r="I75" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="76" spans="1:9">
+      <c r="J75" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>258</v>
       </c>
@@ -4866,8 +5361,14 @@
       <c r="I76" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:9">
+      <c r="J76" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>264</v>
       </c>
@@ -4896,8 +5397,14 @@
       <c r="I77" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="78" spans="1:9">
+      <c r="J77" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K77" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>505</v>
       </c>
@@ -4926,8 +5433,14 @@
       <c r="I78" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="79" spans="1:9">
+      <c r="J78" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>613</v>
       </c>
@@ -4956,8 +5469,14 @@
       <c r="I79" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:9">
+      <c r="J79" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K79" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>274</v>
       </c>
@@ -4986,8 +5505,14 @@
       <c r="I80" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="81" spans="1:9">
+      <c r="J80" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>277</v>
       </c>
@@ -5016,8 +5541,14 @@
       <c r="I81" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="82" spans="1:9">
+      <c r="J81" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>280</v>
       </c>
@@ -5046,8 +5577,14 @@
       <c r="I82" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="83" spans="1:9">
+      <c r="J82" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>285</v>
       </c>
@@ -5076,8 +5613,14 @@
       <c r="I83" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="84" spans="1:9">
+      <c r="J83" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>289</v>
       </c>
@@ -5106,8 +5649,14 @@
       <c r="I84" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:9">
+      <c r="J84" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K84" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
         <v>293</v>
       </c>
@@ -5136,8 +5685,14 @@
       <c r="I85" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="86" spans="1:9">
+      <c r="J85" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
         <v>506</v>
       </c>
@@ -5166,8 +5721,14 @@
       <c r="I86" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="J86" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
         <v>298</v>
       </c>
@@ -5196,8 +5757,14 @@
       <c r="I87" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:9">
+      <c r="J87" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
         <v>299</v>
       </c>
@@ -5226,8 +5793,14 @@
       <c r="I88" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="89" spans="1:9">
+      <c r="J88" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
         <v>300</v>
       </c>
@@ -5256,8 +5829,14 @@
       <c r="I89" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="90" spans="1:9">
+      <c r="J89" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>303</v>
       </c>
@@ -5286,8 +5865,14 @@
       <c r="I90" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="91" spans="1:9">
+      <c r="J90" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K90" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
         <v>308</v>
       </c>
@@ -5316,8 +5901,14 @@
       <c r="I91" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="92" spans="1:9">
+      <c r="J91" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
         <v>615</v>
       </c>
@@ -5346,8 +5937,14 @@
       <c r="I92" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="93" spans="1:9">
+      <c r="J92" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
         <v>508</v>
       </c>
@@ -5376,8 +5973,14 @@
       <c r="I93" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="94" spans="1:9">
+      <c r="J93" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
         <v>317</v>
       </c>
@@ -5406,8 +6009,14 @@
       <c r="I94" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:9">
+      <c r="J94" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
         <v>321</v>
       </c>
@@ -5436,8 +6045,14 @@
       <c r="I95" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="96" spans="1:9">
+      <c r="J95" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
         <v>325</v>
       </c>
@@ -5466,8 +6081,14 @@
       <c r="I96" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="97" spans="1:9">
+      <c r="J96" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" t="s">
         <v>330</v>
       </c>
@@ -5496,8 +6117,14 @@
       <c r="I97" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="98" spans="1:9">
+      <c r="J97" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K97" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" t="s">
         <v>334</v>
       </c>
@@ -5526,8 +6153,14 @@
       <c r="I98" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="99" spans="1:9">
+      <c r="J98" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K98" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
         <v>338</v>
       </c>
@@ -5556,8 +6189,14 @@
       <c r="I99" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="100" spans="1:9">
+      <c r="J99" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K99" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
         <v>341</v>
       </c>
@@ -5586,8 +6225,14 @@
       <c r="I100" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="1:9">
+      <c r="J100" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K100" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
         <v>344</v>
       </c>
@@ -5616,8 +6261,14 @@
       <c r="I101" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="1:9">
+      <c r="J101" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" t="s">
         <v>348</v>
       </c>
@@ -5646,8 +6297,14 @@
       <c r="I102" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="103" spans="1:9">
+      <c r="J102" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
         <v>351</v>
       </c>
@@ -5676,8 +6333,14 @@
       <c r="I103" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="104" spans="1:9">
+      <c r="J103" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" t="s">
         <v>355</v>
       </c>
@@ -5706,8 +6369,14 @@
       <c r="I104" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="105" spans="1:9">
+      <c r="J104" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
         <v>358</v>
       </c>
@@ -5736,8 +6405,14 @@
       <c r="I105" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="106" spans="1:9">
+      <c r="J105" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" t="s">
         <v>361</v>
       </c>
@@ -5766,8 +6441,14 @@
       <c r="I106" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="107" spans="1:9">
+      <c r="J106" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" t="s">
         <v>509</v>
       </c>
@@ -5796,8 +6477,14 @@
       <c r="I107" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="108" spans="1:9">
+      <c r="J107" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" t="s">
         <v>366</v>
       </c>
@@ -5826,8 +6513,14 @@
       <c r="I108" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="109" spans="1:9">
+      <c r="J108" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" t="s">
         <v>370</v>
       </c>
@@ -5856,8 +6549,14 @@
       <c r="I109" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="110" spans="1:9">
+      <c r="J109" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K109" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
         <v>377</v>
       </c>
@@ -5886,8 +6585,14 @@
       <c r="I110" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="111" spans="1:9">
+      <c r="J110" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K110" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111" t="s">
         <v>381</v>
       </c>
@@ -5916,8 +6621,14 @@
       <c r="I111" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="112" spans="1:9">
+      <c r="J111" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K111" s="6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112" t="s">
         <v>386</v>
       </c>
@@ -5946,8 +6657,14 @@
       <c r="I112" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="113" spans="1:9">
+      <c r="J112" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K112" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
         <v>390</v>
       </c>
@@ -5976,8 +6693,14 @@
       <c r="I113" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="114" spans="1:9">
+      <c r="J113" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K113" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
         <v>393</v>
       </c>
@@ -6006,8 +6729,14 @@
       <c r="I114" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="115" spans="1:9">
+      <c r="J114" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
         <v>395</v>
       </c>
@@ -6036,8 +6765,14 @@
       <c r="I115" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="116" spans="1:9">
+      <c r="J115" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
         <v>397</v>
       </c>
@@ -6066,8 +6801,14 @@
       <c r="I116" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="117" spans="1:9">
+      <c r="J116" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
         <v>401</v>
       </c>
@@ -6096,8 +6837,14 @@
       <c r="I117" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="118" spans="1:9">
+      <c r="J117" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
         <v>402</v>
       </c>
@@ -6126,8 +6873,14 @@
       <c r="I118" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="119" spans="1:9">
+      <c r="J118" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
         <v>405</v>
       </c>
@@ -6156,8 +6909,14 @@
       <c r="I119" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="120" spans="1:9">
+      <c r="J119" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K119" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>410</v>
       </c>
@@ -6186,8 +6945,14 @@
       <c r="I120" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="121" spans="1:9">
+      <c r="J120" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K120" s="6" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
         <v>414</v>
       </c>
@@ -6216,8 +6981,14 @@
       <c r="I121" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="122" spans="1:9">
+      <c r="J121" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K121" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" t="s">
         <v>419</v>
       </c>
@@ -6246,8 +7017,14 @@
       <c r="I122" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="123" spans="1:9">
+      <c r="J122" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K122" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123" t="s">
         <v>422</v>
       </c>
@@ -6276,8 +7053,14 @@
       <c r="I123" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="124" spans="1:9">
+      <c r="J123" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K123" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" t="s">
         <v>425</v>
       </c>
@@ -6306,8 +7089,14 @@
       <c r="I124" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="125" spans="1:9">
+      <c r="J124" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
         <v>426</v>
       </c>
@@ -6336,8 +7125,14 @@
       <c r="I125" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="126" spans="1:9">
+      <c r="J125" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K125" s="6" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
         <v>429</v>
       </c>
@@ -6366,8 +7161,14 @@
       <c r="I126" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="127" spans="1:9">
+      <c r="J126" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K126" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
         <v>433</v>
       </c>
@@ -6396,8 +7197,14 @@
       <c r="I127" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="128" spans="1:9">
+      <c r="J127" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K127" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
         <v>436</v>
       </c>
@@ -6426,8 +7233,14 @@
       <c r="I128" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="129" spans="1:9">
+      <c r="J128" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K128" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129" t="s">
         <v>439</v>
       </c>
@@ -6456,8 +7269,14 @@
       <c r="I129" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="130" spans="1:9">
+      <c r="J129" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K129" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" t="s">
         <v>440</v>
       </c>
@@ -6486,8 +7305,14 @@
       <c r="I130" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="131" spans="1:9">
+      <c r="J130" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K130" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131" t="s">
         <v>444</v>
       </c>
@@ -6516,8 +7341,14 @@
       <c r="I131" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="132" spans="1:9">
+      <c r="J131" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K131" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" t="s">
         <v>449</v>
       </c>
@@ -6546,8 +7377,14 @@
       <c r="I132" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="133" spans="1:9">
+      <c r="J132" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K132" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" t="s">
         <v>616</v>
       </c>
@@ -6576,8 +7413,14 @@
       <c r="I133" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="134" spans="1:9">
+      <c r="J133" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K133" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
       <c r="A134" t="s">
         <v>455</v>
       </c>
@@ -6606,8 +7449,14 @@
       <c r="I134" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="135" spans="1:9">
+      <c r="J134" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K134" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
       <c r="A135" t="s">
         <v>459</v>
       </c>
@@ -6636,8 +7485,14 @@
       <c r="I135" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="136" spans="1:9">
+      <c r="J135" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K135" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
       <c r="A136" t="s">
         <v>462</v>
       </c>
@@ -6666,8 +7521,14 @@
       <c r="I136" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="137" spans="1:9">
+      <c r="J136" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K136" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
       <c r="A137" t="s">
         <v>511</v>
       </c>
@@ -6696,8 +7557,14 @@
       <c r="I137" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="138" spans="1:9">
+      <c r="J137" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K137" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
       <c r="A138" t="s">
         <v>469</v>
       </c>
@@ -6726,8 +7593,14 @@
       <c r="I138" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="139" spans="1:9">
+      <c r="J138" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K138" s="6" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
       <c r="A139" t="s">
         <v>513</v>
       </c>
@@ -6756,8 +7629,14 @@
       <c r="I139" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="140" spans="1:9">
+      <c r="J139" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K139" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
       <c r="A140" t="s">
         <v>476</v>
       </c>
@@ -6786,8 +7665,14 @@
       <c r="I140" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="141" spans="1:9">
+      <c r="J140" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K140" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
       <c r="A141" t="s">
         <v>479</v>
       </c>
@@ -6816,8 +7701,14 @@
       <c r="I141" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="142" spans="1:9">
+      <c r="J141" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K141" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
       <c r="A142" t="s">
         <v>483</v>
       </c>
@@ -6846,8 +7737,14 @@
       <c r="I142" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="143" spans="1:9">
+      <c r="J142" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K142" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
       <c r="A143" t="s">
         <v>486</v>
       </c>
@@ -6876,8 +7773,14 @@
       <c r="I143" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="144" spans="1:9">
+      <c r="J143" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K143" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
       <c r="A144" t="s">
         <v>617</v>
       </c>
@@ -6906,8 +7809,14 @@
       <c r="I144" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="145" spans="1:9">
+      <c r="J144" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K144" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
       <c r="A145" t="s">
         <v>514</v>
       </c>
@@ -6936,8 +7845,14 @@
       <c r="I145" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="146" spans="1:9">
+      <c r="J145" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K145" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
       <c r="A146" t="s">
         <v>518</v>
       </c>
@@ -6966,8 +7881,14 @@
       <c r="I146" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="147" spans="1:9">
+      <c r="J146" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K146" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
       <c r="A147" t="s">
         <v>522</v>
       </c>
@@ -6996,8 +7917,14 @@
       <c r="I147" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="148" spans="1:9">
+      <c r="J147" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K147" s="6" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
       <c r="A148" t="s">
         <v>525</v>
       </c>
@@ -7026,8 +7953,14 @@
       <c r="I148" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="149" spans="1:9">
+      <c r="J148" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K148" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
       <c r="A149" t="s">
         <v>529</v>
       </c>
@@ -7056,8 +7989,14 @@
       <c r="I149" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="150" spans="1:9">
+      <c r="J149" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K149" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
       <c r="A150" t="s">
         <v>532</v>
       </c>
@@ -7086,8 +8025,14 @@
       <c r="I150" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="151" spans="1:9">
+      <c r="J150" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K150" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
       <c r="A151" t="s">
         <v>535</v>
       </c>
@@ -7116,8 +8061,14 @@
       <c r="I151" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="152" spans="1:9">
+      <c r="J151" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K151" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
       <c r="A152" t="s">
         <v>539</v>
       </c>
@@ -7146,8 +8097,14 @@
       <c r="I152" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="153" spans="1:9">
+      <c r="J152" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K152" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
       <c r="A153" t="s">
         <v>542</v>
       </c>
@@ -7176,8 +8133,14 @@
       <c r="I153" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="154" spans="1:9">
+      <c r="J153" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K153" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154" t="s">
         <v>546</v>
       </c>
@@ -7206,8 +8169,14 @@
       <c r="I154" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="155" spans="1:9">
+      <c r="J154" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K154" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
       <c r="A155" t="s">
         <v>550</v>
       </c>
@@ -7236,8 +8205,14 @@
       <c r="I155" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="156" spans="1:9">
+      <c r="J155" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K155" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
       <c r="A156" t="s">
         <v>554</v>
       </c>
@@ -7266,8 +8241,14 @@
       <c r="I156" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="157" spans="1:9">
+      <c r="J156" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K156" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
       <c r="A157" t="s">
         <v>557</v>
       </c>
@@ -7296,8 +8277,14 @@
       <c r="I157" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="158" spans="1:9">
+      <c r="J157" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K157" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
       <c r="A158" t="s">
         <v>560</v>
       </c>
@@ -7326,8 +8313,14 @@
       <c r="I158" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="159" spans="1:9">
+      <c r="J158" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K158" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
       <c r="A159" t="s">
         <v>563</v>
       </c>
@@ -7356,8 +8349,14 @@
       <c r="I159" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="160" spans="1:9">
+      <c r="J159" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
       <c r="A160" t="s">
         <v>567</v>
       </c>
@@ -7386,8 +8385,14 @@
       <c r="I160" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="161" spans="1:9">
+      <c r="J160" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
       <c r="A161" t="s">
         <v>570</v>
       </c>
@@ -7416,8 +8421,14 @@
       <c r="I161" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="162" spans="1:9">
+      <c r="J161" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K161" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
       <c r="A162" t="s">
         <v>618</v>
       </c>
@@ -7446,8 +8457,14 @@
       <c r="I162" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="163" spans="1:9">
+      <c r="J162" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K162" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
       <c r="A163" t="s">
         <v>623</v>
       </c>
@@ -7476,8 +8493,14 @@
       <c r="I163" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="164" spans="1:9">
+      <c r="J163" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
       <c r="A164" t="s">
         <v>626</v>
       </c>
@@ -7506,8 +8529,14 @@
       <c r="I164" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="165" spans="1:9">
+      <c r="J164" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K164" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
       <c r="A165" t="s">
         <v>629</v>
       </c>
@@ -7536,8 +8565,14 @@
       <c r="I165" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="166" spans="1:9">
+      <c r="J165" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K165" s="6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
       <c r="A166" t="s">
         <v>632</v>
       </c>
@@ -7566,8 +8601,14 @@
       <c r="I166" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="167" spans="1:9">
+      <c r="J166" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K166" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
       <c r="A167" t="s">
         <v>636</v>
       </c>
@@ -7596,8 +8637,14 @@
       <c r="I167" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="168" spans="1:9">
+      <c r="J167" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K167" s="6" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
       <c r="A168" t="s">
         <v>640</v>
       </c>
@@ -7626,8 +8673,14 @@
       <c r="I168" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="169" spans="1:9">
+      <c r="J168" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K168" s="6" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
       <c r="A169" t="s">
         <v>643</v>
       </c>
@@ -7656,8 +8709,14 @@
       <c r="I169" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="170" spans="1:9">
+      <c r="J169" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K169" s="6" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
       <c r="A170" t="s">
         <v>646</v>
       </c>
@@ -7686,8 +8745,14 @@
       <c r="I170" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="171" spans="1:9">
+      <c r="J170" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K170" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
       <c r="A171" t="s">
         <v>651</v>
       </c>
@@ -7716,8 +8781,14 @@
       <c r="I171" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="172" spans="1:9">
+      <c r="J171" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K171" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
       <c r="A172" t="s">
         <v>654</v>
       </c>
@@ -7746,8 +8817,14 @@
       <c r="I172" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="173" spans="1:9">
+      <c r="J172" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K172" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
       <c r="A173" t="s">
         <v>658</v>
       </c>
@@ -7776,8 +8853,14 @@
       <c r="I173" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="174" spans="1:9">
+      <c r="J173" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K173" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
       <c r="A174" t="s">
         <v>662</v>
       </c>
@@ -7806,8 +8889,14 @@
       <c r="I174" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="175" spans="1:9">
+      <c r="J174" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K174" s="6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
       <c r="A175" t="s">
         <v>666</v>
       </c>
@@ -7836,8 +8925,14 @@
       <c r="I175" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="176" spans="1:9">
+      <c r="J175" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K175" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
       <c r="A176" t="s">
         <v>671</v>
       </c>
@@ -7866,8 +8961,14 @@
       <c r="I176" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="177" spans="1:9">
+      <c r="J176" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K176" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
       <c r="A177" t="s">
         <v>675</v>
       </c>
@@ -7896,8 +8997,14 @@
       <c r="I177" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="178" spans="1:9">
+      <c r="J177" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K177" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
       <c r="A178" t="s">
         <v>679</v>
       </c>
@@ -7926,8 +9033,14 @@
       <c r="I178" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="179" spans="1:9">
+      <c r="J178" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K178" s="6" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
       <c r="A179" t="s">
         <v>683</v>
       </c>
@@ -7956,8 +9069,14 @@
       <c r="I179" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="180" spans="1:9">
+      <c r="J179" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K179" s="6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
       <c r="A180" t="s">
         <v>687</v>
       </c>
@@ -7986,8 +9105,14 @@
       <c r="I180" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="181" spans="1:9">
+      <c r="J180" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
       <c r="A181" t="s">
         <v>690</v>
       </c>
@@ -8016,8 +9141,14 @@
       <c r="I181" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="182" spans="1:9">
+      <c r="J181" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K181" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
       <c r="A182" t="s">
         <v>693</v>
       </c>
@@ -8046,8 +9177,14 @@
       <c r="I182" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="183" spans="1:9">
+      <c r="J182" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K182" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
       <c r="A183" t="s">
         <v>696</v>
       </c>
@@ -8076,8 +9213,14 @@
       <c r="I183" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="184" spans="1:9">
+      <c r="J183" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K183" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
       <c r="A184" t="s">
         <v>699</v>
       </c>
@@ -8106,8 +9249,14 @@
       <c r="I184" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="185" spans="1:9">
+      <c r="J184" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K184" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
       <c r="A185" t="s">
         <v>702</v>
       </c>
@@ -8136,8 +9285,14 @@
       <c r="I185" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="186" spans="1:9">
+      <c r="J185" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K185" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
       <c r="A186" t="s">
         <v>705</v>
       </c>
@@ -8166,8 +9321,14 @@
       <c r="I186" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="187" spans="1:9">
+      <c r="J186" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
       <c r="A187" t="s">
         <v>708</v>
       </c>
@@ -8196,8 +9357,14 @@
       <c r="I187" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="188" spans="1:9">
+      <c r="J187" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K187" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
       <c r="A188" t="s">
         <v>711</v>
       </c>
@@ -8226,8 +9393,14 @@
       <c r="I188" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="189" spans="1:9">
+      <c r="J188" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="K188" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
       <c r="A189" t="s">
         <v>714</v>
       </c>
@@ -8256,8 +9429,14 @@
       <c r="I189" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="190" spans="1:9">
+      <c r="J189" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K189" s="6" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190" t="s">
         <v>717</v>
       </c>
@@ -8286,8 +9465,14 @@
       <c r="I190" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="191" spans="1:9">
+      <c r="J190" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="K190" s="6" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191" t="s">
         <v>720</v>
       </c>
@@ -8316,9 +9501,18 @@
       <c r="I191" t="s">
         <v>8</v>
       </c>
+      <c r="J191" s="1" t="s">
+        <v>727</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="K10:K190">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10:K190">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
